--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -16,9 +16,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <name val="Calibri"/>
@@ -103,11 +101,11 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -531,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>502182540</v>
+        <v>25951644</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>501630140</v>
+        <v>25941773</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>552400</v>
+        <v>9871</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>3.2</v>
+        <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0454</v>
       </c>
     </row>
     <row r="5">
@@ -553,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>502274120</v>
+        <v>25375335</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>501721619</v>
+        <v>25366208</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>552501</v>
+        <v>9127</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0424</v>
       </c>
     </row>
     <row r="6">
@@ -575,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>500656109</v>
+        <v>25188287</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>500105388</v>
+        <v>25179655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>550721</v>
+        <v>8632</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.1256</v>
+        <v>0.0401</v>
       </c>
     </row>
     <row r="7">
@@ -597,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>509267927</v>
+        <v>25281442</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>508707733</v>
+        <v>25273193</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>560194</v>
+        <v>8249</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1297</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="8">
@@ -619,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>508532453</v>
+        <v>25602099</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>507973068</v>
+        <v>25593903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>559385</v>
+        <v>8196</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>3</v>
+        <v>3.13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0373</v>
       </c>
     </row>
     <row r="9">
@@ -641,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>502668286</v>
+        <v>26102543</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>502115351</v>
+        <v>26094204</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>552935</v>
+        <v>8339</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0374</v>
       </c>
     </row>
     <row r="10">
@@ -663,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>489356640</v>
+        <v>26530744</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>488818348</v>
+        <v>26521983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>538292</v>
+        <v>8761</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.134</v>
+        <v>0.0388</v>
       </c>
     </row>
     <row r="11">
@@ -685,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>3514938075</v>
+        <v>180032094</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>3511071647</v>
+        <v>179970919</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>3866428</v>
+        <v>61175</v>
       </c>
       <c r="E11" s="9" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.1297</v>
+        <v>0.0399</v>
       </c>
     </row>
   </sheetData>

--- a/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
+++ b/payhug-spec/_pipeline/investor_admin/_fig/assets/xlsx/일별투자수익_2026-08-21_2026-08-27.xlsx
@@ -529,19 +529,19 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>25951644</v>
+        <v>25970340</v>
       </c>
       <c r="C4" s="4" t="n">
         <v>25941773</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9871</v>
+        <v>28567</v>
       </c>
       <c r="E4" s="5" t="n">
         <v>3.06</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>0.0454</v>
+        <v>0.1315</v>
       </c>
     </row>
     <row r="5">
@@ -551,19 +551,19 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>25375330</v>
+        <v>25394136</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>25366208</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>9127</v>
+        <v>27933</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>3.1</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>0.0424</v>
+        <v>0.1297</v>
       </c>
     </row>
     <row r="6">
@@ -573,19 +573,19 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>25188289</v>
+        <v>25207385</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>25179655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>8632</v>
+        <v>27728</v>
       </c>
       <c r="E6" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>0.0401</v>
+        <v>0.129</v>
       </c>
     </row>
     <row r="7">
@@ -595,19 +595,19 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>25281449</v>
+        <v>25301031</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>25273193</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>8249</v>
+        <v>27831</v>
       </c>
       <c r="E7" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0381</v>
+        <v>0.1287</v>
       </c>
     </row>
     <row r="8">
@@ -617,19 +617,19 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>25602105</v>
+        <v>25622093</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>25593903</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>8196</v>
+        <v>28184</v>
       </c>
       <c r="E8" s="5" t="n">
         <v>3.13</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.0374</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="9">
@@ -639,19 +639,19 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>26102548</v>
+        <v>26122944</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>26094204</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>8339</v>
+        <v>28735</v>
       </c>
       <c r="E9" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.0373</v>
+        <v>0.1286</v>
       </c>
     </row>
     <row r="10">
@@ -661,19 +661,19 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>26530746</v>
+        <v>26551191</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>26521983</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>8761</v>
+        <v>29206</v>
       </c>
       <c r="E10" s="5" t="n">
         <v>3.11</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.0388</v>
+        <v>0.1294</v>
       </c>
     </row>
     <row r="11">
@@ -683,19 +683,19 @@
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>180032111</v>
+        <v>180169120</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>179970919</v>
       </c>
       <c r="D11" s="8" t="n">
-        <v>61175</v>
+        <v>198184</v>
       </c>
       <c r="E11" s="9" t="n">
         <v>3.11</v>
       </c>
       <c r="F11" s="10" t="n">
-        <v>0.0399</v>
+        <v>0.1293</v>
       </c>
     </row>
   </sheetData>
